--- a/data/trans_orig/IP07C20-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C20-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18653</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31155</t>
+          <t>30167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>25216</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13578</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15577</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>17996</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>29131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43814</t>
+          <t>44098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8625</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11893</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>22823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>25254</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41437</t>
+          <t>42746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33849</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48815</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65057</t>
+          <t>64534</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86641</t>
+          <t>85875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>32472</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>39241</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58076</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,47 +3167,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,5%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>7730</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>12798</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>7730</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>3947</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>12853</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14462</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>31439</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>36245</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52464</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23909</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>12853</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>24939</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>29939</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45444</t>
+          <t>45583</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>19607</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>11232</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>26832</t>
+          <t>25636</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>579</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>46564</t>
+          <t>46946</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>68599</t>
+          <t>67658</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>64705</t>
+          <t>64620</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>88596</t>
+          <t>87958</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>117222</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>149242</t>
+          <t>149396</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>111792</t>
+          <t>109612</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>136753</t>
+          <t>138157</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>107129</t>
+          <t>107463</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>134196</t>
+          <t>134917</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>224454</t>
+          <t>225742</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>263405</t>
+          <t>264043</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>80729</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>68489</t>
+          <t>69739</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>94215</t>
+          <t>93247</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>132471</t>
+          <t>132936</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>167357</t>
+          <t>166937</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6880</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>18759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>20783</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>24329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37203</t>
+          <t>37275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,41%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21202</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,21%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33372</t>
+          <t>32704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>16556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13946</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36682</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>14852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>24519</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24322</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38889</t>
+          <t>39262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56405</t>
+          <t>56469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78685</t>
+          <t>77967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24338</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>39604</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>48928</t>
+          <t>48932</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71167</t>
+          <t>71250</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7989,7 +7989,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31055</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49812</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>7676</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10602</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15775</t>
+          <t>15869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>29637</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27572</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>32953</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>33612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>61640</t>
+          <t>61480</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29219</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>29877</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48255</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9494</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>6944</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>14693</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27058</t>
+          <t>26997</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20787</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>94381</t>
+          <t>95381</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>122129</t>
+          <t>123648</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>87334</t>
+          <t>88647</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>114459</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>189816</t>
+          <t>190477</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>229410</t>
+          <t>230868</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>91958</t>
+          <t>92288</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>120136</t>
+          <t>118301</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>98459</t>
+          <t>99090</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>125681</t>
+          <t>126615</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>197254</t>
+          <t>198400</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>235989</t>
+          <t>237155</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>55833</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>80251</t>
+          <t>80570</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>55605</t>
+          <t>55398</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>78157</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>116903</t>
+          <t>117024</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>152417</t>
+          <t>150549</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>16168</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>23283</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7129</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>14641</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19145</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20841</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>19175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>15521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30221</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13184</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>14963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13291</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25480</t>
+          <t>26073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>21421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>32032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25902</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>39726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20762</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36845</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49079</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41044</t>
+          <t>41524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53300</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75591</t>
+          <t>77056</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43661</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21505</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36913</t>
+          <t>36874</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>53048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>75497</t>
+          <t>74907</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19090</t>
+          <t>19396</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19416</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34190</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58634</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32718</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>35321</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53694</t>
+          <t>53215</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>25519</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8068</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19094</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19936</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>33228</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>772</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>70830</t>
+          <t>71534</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>98902</t>
+          <t>97822</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>71790</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>97952</t>
+          <t>96486</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>147997</t>
+          <t>149354</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>185185</t>
+          <t>184552</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>91014</t>
+          <t>90051</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>119153</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>113139</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>143203</t>
+          <t>142004</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>210939</t>
+          <t>212578</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>254079</t>
+          <t>252223</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>83097</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>110801</t>
+          <t>109858</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>77448</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>104979</t>
+          <t>104796</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>166514</t>
+          <t>168199</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>205573</t>
+          <t>206453</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>39782</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>61058</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>28241</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
